--- a/04_DESIGN_TABLES/DesignTable_2502.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2502.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -541,6 +541,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -708,12 +713,17 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p025-t02: agrees on M1@DRIVE, N1@DRIVE, Y1@DRIVE, D@BORE</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2502-04-04-FG</t>
         </is>
       </c>
     </row>
@@ -940,12 +950,17 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p025-t02: agrees on M1@DRIVE, N1@DRIVE, Y1@DRIVE, D@BORE</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2502-06-04-FG</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1411,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1406,7 +1421,7 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>legs diverge from MS51506 A8-8: AW M1=1.52/N1=1.23 vs MS 1.38/1.23 - AW stands, Brennan tiebreak pending</t>
+          <t>legs diverge from MS51506 A8-8: AW M1=1.52/N1=1.23 vs MS 1.38/1.23 - AW stands, Brennan tiebreak pending | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on Y1@DRIVE=1.06~1.062; D@BORE=0.39~0.391</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2492,6 +2507,142 @@
       <c r="O38" t="inlineStr">
         <is>
           <t>2502-32-32-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2502-04-06-FG</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2502-04-06-FG</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>7/16-20 (JIC 37) x 3/8-18 (NPTF female)</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; M1 / N1 / flats / bore: OMi WebsitePartsInfo2026 Items (= Brennan TFA p.25, one source); tap drill = Air-Way per size (A1); JIC end MS33656J</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; legs / flats / bore from OMi Items (= Brennan TFA p.25, one source); end details from the end library</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2502-04-06-FG</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>OMI</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2502-05-04-FG</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2502-05-04-FG</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1/2-20 (JIC 37) x 1/4-18 (NPTF female)</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; M1 / N1 / flats / bore: OMi WebsitePartsInfo2026 Items (= Brennan TFA p.25, one source); tap drill = Air-Way per size (A1); JIC end MS33656J</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; legs / flats / bore from OMi Items (= Brennan TFA p.25, one source); end details from the end library</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2502-05-04-FG</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_2502.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2502.xlsx
@@ -2257,24 +2257,50 @@
           <t>2502-06-08-FG</t>
         </is>
       </c>
+      <c r="B32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.84</v>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>2502-06-08-FG</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>9/16-18 (JIC 37) x 1/2-14 (NPTF female)</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2502-06-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>OMi catalog SKU; M1 / N1 / flats / bore: OMi WebsitePartsInfo2026 Items row 736 (= Brennan TFA p.25, one source) - Air-Way s122 prints only the non-forged 2502-06-08 (forged rule: not used); tap drill = Air-Way per size (A1); JIC end MS33656J</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2502-06-08 dims are NOT assumed; confirm before modelling</t>
+          <t>2026-10-20 (batch 19 E_gen, A7): sizes from OMi Items (= Brennan TFA p.25), end details from the end library</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2285,6 +2311,11 @@
       <c r="O32" t="inlineStr">
         <is>
           <t>2502-06-08-FG</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>
@@ -2368,24 +2399,50 @@
           <t>2502-16-20-FG</t>
         </is>
       </c>
+      <c r="B35" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.66</v>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>2502-16-20-FG</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (JIC 37) x 1 1/4-11 1/2 (NPTF female)</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2502-16-20 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>OMi catalog SKU; M1 / N1 / flats / bore: OMi WebsitePartsInfo2026 Items row 745 (= Brennan TFA p.25, one source) - Air-Way s122 prints only the non-forged 2502-16-20 (forged rule: not used); tap drill = Air-Way per size (A1); JIC end MS33656J</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2502-16-20 dims are NOT assumed; confirm before modelling</t>
+          <t>2026-10-20 (batch 19 E_gen, A7): sizes from OMi Items (= Brennan TFA p.25), end details from the end library</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2396,6 +2453,11 @@
       <c r="O35" t="inlineStr">
         <is>
           <t>2502-16-20-FG</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2611,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2617,7 +2679,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
